--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.6766387053008</v>
+        <v>8.234953789611382</v>
       </c>
       <c r="D2" t="n">
-        <v>8.689426210979367</v>
+        <v>1.412031759284147</v>
       </c>
       <c r="E2" t="n">
-        <v>17.99380358274768</v>
+        <v>2.9239930821965</v>
       </c>
       <c r="F2" t="n">
-        <v>19.10223445464855</v>
+        <v>3.10411309888039</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.369106793020597</v>
+        <v>1.197479853865847</v>
       </c>
       <c r="D3" t="n">
-        <v>7.71367994927569</v>
+        <v>1.2534729917573</v>
       </c>
       <c r="E3" t="n">
-        <v>17.99380358274768</v>
+        <v>2.9239930821965</v>
       </c>
       <c r="F3" t="n">
-        <v>19.10223445464855</v>
+        <v>3.10411309888039</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.89489355460379</v>
+        <v>6.970420202623116</v>
       </c>
       <c r="D4" t="n">
-        <v>40.33989592382299</v>
+        <v>6.555233087621237</v>
       </c>
       <c r="E4" t="n">
-        <v>17.99380358274768</v>
+        <v>2.9239930821965</v>
       </c>
       <c r="F4" t="n">
-        <v>19.10223445464855</v>
+        <v>3.10411309888039</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.81416007090511</v>
+        <v>5.33230101152208</v>
       </c>
       <c r="D5" t="n">
-        <v>33.69091164879787</v>
+        <v>5.474773142929653</v>
       </c>
       <c r="E5" t="n">
-        <v>17.99380358274768</v>
+        <v>2.9239930821965</v>
       </c>
       <c r="F5" t="n">
-        <v>19.10223445464855</v>
+        <v>3.10411309888039</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.82638761661398</v>
+        <v>5.821787987699771</v>
       </c>
       <c r="D6" t="n">
-        <v>35.66998451954413</v>
+        <v>5.796372484425921</v>
       </c>
       <c r="E6" t="n">
-        <v>17.99380358274768</v>
+        <v>2.9239930821965</v>
       </c>
       <c r="F6" t="n">
-        <v>19.10223445464855</v>
+        <v>3.10411309888039</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.95974283070214</v>
+        <v>7.468458209989098</v>
       </c>
       <c r="D7" t="n">
-        <v>46.85092333246297</v>
+        <v>7.613275041525233</v>
       </c>
       <c r="E7" t="n">
-        <v>17.99380358274768</v>
+        <v>2.9239930821965</v>
       </c>
       <c r="F7" t="n">
-        <v>19.10223445464855</v>
+        <v>3.10411309888039</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.86963011178272</v>
+        <v>2.903814893164693</v>
       </c>
       <c r="D8" t="n">
-        <v>17.0007166154266</v>
+        <v>2.762616450006823</v>
       </c>
       <c r="E8" t="n">
-        <v>17.99380358274768</v>
+        <v>2.9239930821965</v>
       </c>
       <c r="F8" t="n">
-        <v>19.10223445464855</v>
+        <v>3.10411309888039</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>69.10267597424127</v>
+        <v>11.22918484581421</v>
       </c>
       <c r="D9" t="n">
-        <v>67.42290150212995</v>
+        <v>10.95622149409612</v>
       </c>
       <c r="E9" t="n">
-        <v>17.99380358274768</v>
+        <v>2.9239930821965</v>
       </c>
       <c r="F9" t="n">
-        <v>19.10223445464855</v>
+        <v>3.10411309888039</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
